--- a/facit/StructureDefinition-SkyddadIdentitet.xlsx
+++ b/facit/StructureDefinition-SkyddadIdentitet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:42:16+00:00</t>
+    <t>2026-10-28T21:54:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
